--- a/templates/template_berna.xlsx
+++ b/templates/template_berna.xlsx
@@ -9,16 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factura" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="ClaveProdServ">[1]Hoja2!$A$2470:$A$55292</definedName>
-    <definedName name="ClavesUnidad">[1]Hoja2!$A$50:$A$2467</definedName>
-    <definedName name="CondicionesdePago">[1]Hoja2!$A$55294:$A$55295</definedName>
-    <definedName name="FormadePago">[1]Hoja2!$A$24:$A$44</definedName>
-    <definedName name="MetododePago">[1]Hoja2!$A$46:$A$47</definedName>
-  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -800,19 +790,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Hoja2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
